--- a/processed_ruby_restored_xlsx/sc131_凛１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc131_凛１：風呂.ss.xlsx
@@ -606,8 +606,8 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>With my eyes shut, I hear the sound of water splashing
-right next to me.</t>
+          <t>With my eyes shut, I hear the sound of water
+splashing right next to me.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -758,8 +758,8 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>I was humming the school song with my eyes closed when
-I suddenly felt someone and opened my eyes.</t>
+          <t>I was humming the school song with my eyes closed
+when I suddenly felt someone and opened my eyes.</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -941,8 +941,9 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Not knowing why Rin-chan is here or what I should even
-say, I glance at her out of the corner of my eye.</t>
+          <t>Not knowing why Rin-chan is here or what I should
+even say, I glance at her out of the corner of my
+eye.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1202,8 +1203,8 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>There has to be some reason Rin-chan got into the bath
-even though I'm here.</t>
+          <t>There has to be some reason Rin-chan got into the
+bath even though I'm here.</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1552,8 +1553,8 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is even more taciturn than usual, and I don't
-know what to do.</t>
+          <t>Rin-chan is even more taciturn than usual, and I
+don't know what to do.</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1829,8 +1830,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan sinks down and submerges half her face in the
-water.</t>
+          <t>Rin-chan sinks down and submerges half her face in
+the water.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2135,8 +2136,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>She avoided meeting my eyes... still, she looked up at
-me a few times like she couldn't help it.</t>
+          <t>She avoided meeting my eyes... still, she looked up
+at me a few times like she couldn't help it.</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2380,8 +2381,8 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Or rather, it seemed like she was playing some kind of
-make-believe game.</t>
+          <t>Or rather, it seemed like she was playing some kind
+of make-believe game.</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2684,9 +2685,9 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>I've been purposely trying not to think about it until
-now, but with Rin-chan naked here, I just can't help
-getting hard...</t>
+          <t>I've been purposely trying not to think about it
+until now, but with Rin-chan naked here, I just can't
+help getting hard...</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2762,8 +2763,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Ugh... I've thought it before, but Rin-chan's feelings
-are always complicated.</t>
+          <t>Ugh... I've thought it before, but Rin-chan's
+feelings are always complicated.</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3005,8 +3006,8 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>When I asked, deliberately vague, Rin-chan fumbled for
-a moment and then tried to cover it up.</t>
+          <t>When I asked, deliberately vague, Rin-chan fumbled
+for a moment and then tried to cover it up.</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3127,9 +3128,9 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan couldn’t hide her intense curiosity, and with
-her face flushed bright red she stared fixedly at the
-penis.</t>
+          <t>Rin-chan couldn’t hide her intense curiosity, and
+with her face flushed bright red she stared fixedly
+at the penis.</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3588,8 +3589,8 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>I give a wry smile to mean 'don't worry about it,' and
-Rin-chan peeks out from under my arm.</t>
+          <t>I give a wry smile to mean 'don't worry about it,'
+and Rin-chan peeks out from under my arm.</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -4655,7 +4656,8 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan looks up at me with an apologetic expression.</t>
+          <t>Rin-chan looks up at me with an apologetic
+expression.</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -5069,8 +5071,8 @@
       <c r="B302" s="1" t="inlineStr">
         <is>
           <t>Rin-chan, making onomatopoeic sounds that end up
-sounding embarrassed, still does her best to stroke me
-shiko-shiko.</t>
+sounding embarrassed, still does her best to stroke
+me shiko-shiko.</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5131,7 +5133,8 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... don't squeeze, scrub-scrub, stroke-stroke...」</t>
+          <t>「Yeah... don't squeeze, scrub-scrub,
+stroke-stroke...」</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5283,8 +5286,8 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>...Maybe asking her to say things out loud earlier was
-the right call.</t>
+          <t>...Maybe asking her to say things out loud earlier
+was the right call.</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -7070,9 +7073,9 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>It was only the pinky, but when the ring finger joined
-in, the stimulation doubled... and it swelled up all
-at once！</t>
+          <t>It was only the pinky, but when the ring finger
+joined in, the stimulation doubled... and it swelled
+up all at once！</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -7389,8 +7392,8 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t>Even with the same stroke as before, my sensitivity is
-multiplied...！</t>
+          <t>Even with the same stroke as before, my sensitivity
+is multiplied...！</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7694,8 +7697,8 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>She could clearly tell it wouldn't end with just heavy
-breathing anymore.</t>
+          <t>She could clearly tell it wouldn't end with just
+heavy breathing anymore.</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7971,8 +7974,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>She hooks her pinky on the head and rubs the underside
-repeatedly with the pad of her finger.</t>
+          <t>She hooks her pinky on the head and rubs the
+underside repeatedly with the pad of her finger.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8093,8 +8096,8 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's actions suddenly become more intense all at
-once.</t>
+          <t>Rin-chan's actions suddenly become more intense all
+at once.</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -8124,8 +8127,8 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>Each time the stimulated penis receives that touch, it
-bounces up.</t>
+          <t>Each time the stimulated penis receives that touch,
+it bounces up.</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8171,8 +8174,8 @@
       </c>
       <c r="B505" s="1" t="inlineStr">
         <is>
-          <t>She squeezes while rubbing, and even when she loosens,
-she keeps rubbing…</t>
+          <t>She squeezes while rubbing, and even when she
+loosens, she keeps rubbing…</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -8405,7 +8408,8 @@
         <is>
           <t>Watched closely and rubbed thoroughly... finally the
 tip was relentlessly teased, and the penis, pushed
-past its limit, spewed out an almost overflowing load！</t>
+past its limit, spewed out an almost overflowing
+load！</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8466,8 +8470,8 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>Got carried away and kept stroking my penis even while
-I was ejaculating…！</t>
+          <t>Got carried away and kept stroking my penis even
+while I was ejaculating…！</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8605,7 +8609,8 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh！ Rin-chan, nnna！ Please... ah！ Ah！ Nnuuaaahhh！」</t>
+          <t>「Aahhh！ Rin-chan, nnna！ Please... ah！ Ah！
+Nnuuaaahhh！」</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8846,8 +8851,8 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>Rin, maybe thinking she’d gone too far because she got
-carried away, looked at me with worry.</t>
+          <t>Rin, maybe thinking she’d gone too far because she
+got carried away, looked at me with worry.</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -8893,8 +8898,8 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>I answered with my head still fuzzy... and stared back
-at Rin.</t>
+          <t>I answered with my head still fuzzy... and stared
+back at Rin.</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -9171,8 +9176,8 @@
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
-          <t>She's fine when she's on the offensive, but she really
-can't take being on the receiving end...</t>
+          <t>She's fine when she's on the offensive, but she
+really can't take being on the receiving end...</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -9266,8 +9271,8 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>Not knowing how I felt, Rin-chan was trembling, scared
-of when I might strike back.</t>
+          <t>Not knowing how I felt, Rin-chan was trembling,
+scared of when I might strike back.</t>
         </is>
       </c>
       <c r="C576" t="n">

--- a/processed_ruby_restored_xlsx/sc131_凛１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc131_凛１：風呂.ss.xlsx
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Still, she watches me stroking my penis and gives a
+          <t>Still, she watches him stroking his penis and gives a
 small, repeated nod.</t>
         </is>
       </c>
@@ -7057,8 +7057,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>I scoop it up with a finger, mixing it lewdly as I
-smear a generous amount onto the tip.</t>
+          <t>He scoops it up with a finger, mixing it lewdly as he
+smears a generous amount onto the tip.</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -8375,8 +8375,8 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ahhh！ Ahhh, haaah！ I'm coming, I'm gonna...
-uuuuuu！」</t>
+          <t>Ah, ahhh！ Ahhh, haaah！ I'm coming, I'm gonna...
+uuuuuu！</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>Even though I'm spraying white fluid all over... I
+          <t>Even though I'm spraying white fluid all over... he
 still won't stop jerking me off！</t>
         </is>
       </c>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>「Fuh, ah... aaaaaah... uuu...」</t>
+          <t>Fuh, ah... aaaaaah... uuu...</t>
         </is>
       </c>
       <c r="C537" t="n">
